--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro/Desktop/SendMail/SendMailData/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260A5A09-7DFB-45A0-B614-40747F8EEB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4913E9D0-84B4-4F4E-A42E-668FAE34BF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="768" windowWidth="23256" windowHeight="12456" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20660" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>Horas Soporte Merpes</t>
   </si>
@@ -302,7 +301,10 @@
     <t>FEBRERO</t>
   </si>
   <si>
-    <t>desarrolloweb2@grupomerpes.com</t>
+    <t>jeisoncardozo@outlook.com</t>
+  </si>
+  <si>
+    <t>suarezjeisoncardozo@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -584,6 +586,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -605,10 +608,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -973,39 +975,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A7959B-608A-4897-ABDC-AE81B68A9DCE}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="83.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="83.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="16" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1040,7 +1042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1081,7 +1083,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -1118,9 +1120,11 @@
         <f t="shared" ref="K4:K45" si="2">I4-J4</f>
         <v>11</v>
       </c>
-      <c r="L4" s="23"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
@@ -1237,7 +1241,7 @@
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
@@ -1354,7 +1358,7 @@
       </c>
       <c r="L10" s="9"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
@@ -1391,9 +1395,9 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -1432,7 +1436,7 @@
       </c>
       <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -1510,7 +1514,7 @@
       </c>
       <c r="L14" s="9"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
@@ -1549,7 +1553,7 @@
       </c>
       <c r="L15" s="9"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1588,7 +1592,7 @@
       </c>
       <c r="L16" s="9"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -1627,7 +1631,7 @@
       </c>
       <c r="L17" s="15"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
@@ -1666,7 +1670,7 @@
       </c>
       <c r="L18" s="9"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="L19" s="9"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -1744,7 +1748,7 @@
       </c>
       <c r="L20" s="13"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
@@ -1783,7 +1787,7 @@
       </c>
       <c r="L21" s="9"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>44</v>
       </c>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>46</v>
       </c>
@@ -1861,7 +1865,7 @@
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>48</v>
       </c>
@@ -1900,7 +1904,7 @@
       </c>
       <c r="L24" s="9"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
@@ -1939,7 +1943,7 @@
       </c>
       <c r="L25" s="11"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>50</v>
       </c>
@@ -1978,7 +1982,7 @@
       </c>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
@@ -2017,7 +2021,7 @@
       </c>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>54</v>
       </c>
@@ -2056,7 +2060,7 @@
       </c>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
@@ -2095,7 +2099,7 @@
       </c>
       <c r="L29" s="9"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>57</v>
       </c>
@@ -2134,7 +2138,7 @@
       </c>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>59</v>
       </c>
@@ -2173,7 +2177,7 @@
       </c>
       <c r="L31" s="11"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>61</v>
       </c>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="L32" s="11"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
@@ -2251,7 +2255,7 @@
       </c>
       <c r="L33" s="9"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="L34" s="11"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>85</v>
       </c>
@@ -2329,7 +2333,7 @@
       </c>
       <c r="L35" s="15"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
@@ -2368,7 +2372,7 @@
       </c>
       <c r="L36" s="9"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>69</v>
       </c>
@@ -2407,7 +2411,7 @@
       </c>
       <c r="L37" s="9"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>70</v>
       </c>
@@ -2446,7 +2450,7 @@
       </c>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>70</v>
       </c>
@@ -2485,7 +2489,7 @@
       </c>
       <c r="L39" s="9"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>72</v>
       </c>
@@ -2524,7 +2528,7 @@
       </c>
       <c r="L40" s="9"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>74</v>
       </c>
@@ -2563,7 +2567,7 @@
       </c>
       <c r="L41" s="9"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>74</v>
       </c>
@@ -2602,7 +2606,7 @@
       </c>
       <c r="L42" s="9"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
@@ -2641,7 +2645,7 @@
       </c>
       <c r="L43" s="11"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>79</v>
       </c>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="L44" s="11"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>79</v>
       </c>
@@ -2719,11 +2723,11 @@
       </c>
       <c r="L45" s="11"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="22"/>
+      <c r="B46" s="23"/>
       <c r="C46" s="10">
         <f t="shared" ref="C46:K46" si="3">SUM(C3:C45)</f>
         <v>366</v>
@@ -2787,6 +2791,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" xr:uid="{8E1ACFA4-2EDE-4A57-A8D1-FBFF460DD8DB}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{FAEB5CFE-1725-C049-81F5-4BA996AE4248}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro/Desktop/SendMail/SendMailData/datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4913E9D0-84B4-4F4E-A42E-668FAE34BF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AAE890-B1F4-4DB5-AB62-894DD0B68F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20660" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
+    <workbookView xWindow="-23040" yWindow="1824" windowWidth="21600" windowHeight="11292" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -301,17 +302,17 @@
     <t>FEBRERO</t>
   </si>
   <si>
-    <t>jeisoncardozo@outlook.com</t>
-  </si>
-  <si>
-    <t>suarezjeisoncardozo@gmail.com</t>
+    <t>desarrolloweb2@grupomerpes.com</t>
+  </si>
+  <si>
+    <t>jefediseno@grupomerpes.com; kupaa@grupomerpes.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,6 +361,14 @@
       <family val="2"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF467886"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -374,9 +383,8 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -545,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -570,13 +578,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
@@ -586,7 +592,10 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,7 +619,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -975,39 +984,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A7959B-608A-4897-ABDC-AE81B68A9DCE}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="83.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="83.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="17" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
       <c r="L1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1079,11 +1088,9 @@
         <f>I3-J3</f>
         <v>14</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -1120,11 +1127,9 @@
         <f t="shared" ref="K4:K45" si="2">I4-J4</f>
         <v>11</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
@@ -1161,9 +1166,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L5" s="11"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1200,9 +1205,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
@@ -1239,9 +1244,9 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1278,9 +1283,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
@@ -1356,9 +1361,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
@@ -1395,9 +1400,11 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="L11" s="16"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L11" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
@@ -1434,9 +1441,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1475,7 +1482,7 @@
       </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -1512,9 +1519,11 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
@@ -1551,9 +1560,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -1590,9 +1599,9 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>34</v>
       </c>
@@ -1631,7 +1640,7 @@
       </c>
       <c r="L17" s="15"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
@@ -1668,9 +1677,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
@@ -1707,9 +1716,9 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
@@ -1748,7 +1757,7 @@
       </c>
       <c r="L20" s="13"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
@@ -1785,9 +1794,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>44</v>
       </c>
@@ -1824,9 +1833,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="12"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="16"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>46</v>
       </c>
@@ -1865,7 +1874,7 @@
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>48</v>
       </c>
@@ -1902,9 +1911,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>50</v>
       </c>
@@ -1941,9 +1950,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>50</v>
       </c>
@@ -1980,9 +1989,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="11"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>52</v>
       </c>
@@ -2019,9 +2028,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>54</v>
       </c>
@@ -2058,9 +2067,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>55</v>
       </c>
@@ -2097,9 +2106,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L29" s="9"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>57</v>
       </c>
@@ -2136,9 +2145,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>59</v>
       </c>
@@ -2175,9 +2184,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L31" s="11"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>61</v>
       </c>
@@ -2214,9 +2223,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L32" s="11"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="12"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
@@ -2253,9 +2262,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
@@ -2292,9 +2301,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L34" s="11"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="12"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>85</v>
       </c>
@@ -2333,7 +2342,7 @@
       </c>
       <c r="L35" s="15"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
@@ -2370,9 +2379,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="9"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>69</v>
       </c>
@@ -2409,9 +2418,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L37" s="10"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>70</v>
       </c>
@@ -2450,7 +2459,7 @@
       </c>
       <c r="L38" s="14"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>70</v>
       </c>
@@ -2487,9 +2496,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L39" s="9"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L39" s="10"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>72</v>
       </c>
@@ -2526,9 +2535,9 @@
         <f>I40-J40</f>
         <v>-1</v>
       </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L40" s="10"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>74</v>
       </c>
@@ -2565,9 +2574,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="10"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2613,9 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="10"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
@@ -2643,9 +2652,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>79</v>
       </c>
@@ -2682,9 +2691,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L44" s="11"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="12"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>79</v>
       </c>
@@ -2721,18 +2730,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L45" s="11"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="23" t="s">
+      <c r="L45" s="12"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="10">
+      <c r="B46" s="24"/>
+      <c r="C46" s="11">
         <f t="shared" ref="C46:K46" si="3">SUM(C3:C45)</f>
         <v>366</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="11">
         <f t="shared" si="3"/>
         <v>83.1</v>
       </c>
@@ -2740,31 +2749,31 @@
         <f t="shared" si="3"/>
         <v>282.90000000000003</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="11">
         <f t="shared" si="3"/>
         <v>181</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="11">
         <f>SUM(G3:G45)</f>
         <v>68.999999999999986</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="11">
         <f t="shared" si="3"/>
         <v>112.00000000000001</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="11">
         <f t="shared" si="3"/>
         <v>295</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="11">
         <f>SUM(J3:J45)</f>
         <v>100</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="11">
         <f t="shared" si="3"/>
         <v>195</v>
       </c>
-      <c r="L46" s="9"/>
+      <c r="L46" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2790,8 +2799,7 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{8E1ACFA4-2EDE-4A57-A8D1-FBFF460DD8DB}"/>
-    <hyperlink ref="L4" r:id="rId2" xr:uid="{FAEB5CFE-1725-C049-81F5-4BA996AE4248}"/>
+    <hyperlink ref="L11" r:id="rId1" xr:uid="{988AEE33-2668-4C2B-A5D5-7F2783D7A14D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AAE890-B1F4-4DB5-AB62-894DD0B68F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A55FB11-8872-4F8A-B6DB-ED27C34BAF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23040" yWindow="1824" windowWidth="21600" windowHeight="11292" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
   <si>
     <t>Horas Soporte Merpes</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>jefediseno@grupomerpes.com; kupaa@grupomerpes.com</t>
+  </si>
+  <si>
+    <t>desarrolloweb3@grupomerpes.com</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,7 +598,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -993,25 +995,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="18" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
       <c r="L1" t="s">
         <v>3</v>
       </c>
@@ -1441,7 +1443,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L12" s="17"/>
+      <c r="L12" s="6" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -1480,7 +1484,9 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L13" s="6"/>
+      <c r="L13" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -1519,9 +1525,7 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L14" s="10" t="s">
-        <v>89</v>
-      </c>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
@@ -2733,10 +2737,10 @@
       <c r="L45" s="12"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="24"/>
+      <c r="B46" s="23"/>
       <c r="C46" s="11">
         <f t="shared" ref="C46:K46" si="3">SUM(C3:C45)</f>
         <v>366</v>
@@ -2800,6 +2804,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="L11" r:id="rId1" xr:uid="{988AEE33-2668-4C2B-A5D5-7F2783D7A14D}"/>
+    <hyperlink ref="L12" r:id="rId2" xr:uid="{FCB11EAA-00FE-4196-8174-2E064FD40AEC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A55FB11-8872-4F8A-B6DB-ED27C34BAF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3390AAA4-E3D4-42B0-AF25-62E3F30CDE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23040" yWindow="1824" windowWidth="21600" windowHeight="11292" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
   <si>
     <t>Horas Soporte Merpes</t>
   </si>
@@ -303,12 +303,6 @@
   </si>
   <si>
     <t>desarrolloweb2@grupomerpes.com</t>
-  </si>
-  <si>
-    <t>jefediseno@grupomerpes.com; kupaa@grupomerpes.com</t>
-  </si>
-  <si>
-    <t>desarrolloweb3@grupomerpes.com</t>
   </si>
 </sst>
 </file>
@@ -1443,9 +1437,7 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>90</v>
-      </c>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -1484,9 +1476,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>89</v>
-      </c>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -2804,7 +2794,6 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="L11" r:id="rId1" xr:uid="{988AEE33-2668-4C2B-A5D5-7F2783D7A14D}"/>
-    <hyperlink ref="L12" r:id="rId2" xr:uid="{FCB11EAA-00FE-4196-8174-2E064FD40AEC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3390AAA4-E3D4-42B0-AF25-62E3F30CDE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60339DE-C64B-44E4-AD4E-D8FBAE4791DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23040" yWindow="1824" windowWidth="21600" windowHeight="11292" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
@@ -550,7 +550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -592,6 +592,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -612,6 +613,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -989,25 +993,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="17" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
       <c r="L1" t="s">
         <v>3</v>
       </c>
@@ -1476,7 +1480,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L13" s="6"/>
+      <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -1632,7 +1636,7 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="L17" s="15"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -2727,10 +2731,10 @@
       <c r="L45" s="12"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B46" s="23"/>
+      <c r="B46" s="24"/>
       <c r="C46" s="11">
         <f t="shared" ref="C46:K46" si="3">SUM(C3:C45)</f>
         <v>366</v>

--- a/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
+++ b/datos/CONSOLIDADO HORAS SOPORTE - DESARROLLO FEBRERO 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeisson Cardoso\Desktop\envio-correos\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60339DE-C64B-44E4-AD4E-D8FBAE4791DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35628FEA-505E-41D5-93A8-ABDCD06D0F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23040" yWindow="1824" windowWidth="21600" windowHeight="11292" xr2:uid="{4CE814AB-A5DA-4E46-8F9F-8A1DE2EE5F3B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
   <si>
     <t>Horas Soporte Merpes</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>desarrolloweb2@grupomerpes.com</t>
+  </si>
+  <si>
+    <t>kupaa@grupomerpes.com</t>
   </si>
 </sst>
 </file>
@@ -550,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -592,7 +595,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -613,9 +618,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1480,7 +1482,9 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L13" s="17"/>
+      <c r="L13" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -1636,7 +1640,7 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="L17" s="25"/>
+      <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -2798,6 +2802,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="L11" r:id="rId1" xr:uid="{988AEE33-2668-4C2B-A5D5-7F2783D7A14D}"/>
+    <hyperlink ref="L13" r:id="rId2" xr:uid="{9B80899A-8A8A-4010-9CA2-BEAB607A650B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
